--- a/media/price_lists/refrigeracion_norte.xlsx
+++ b/media/price_lists/refrigeracion_norte.xlsx
@@ -22074,12 +22074,12 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>3027-2023-3</t>
+          <t>535-5020-0</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>PLAQUETA POTENCIA GAFA/ELECTROLUX 6000/7000/6500/7500</t>
+          <t>RODAMIENTO NSK 35 BG05 35 X 50 X 20 (JAPON)</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -22132,12 +22132,12 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>504-9803389-9</t>
+          <t>3027-2023-3</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>PLAQUETA DISPLAY LED DREAN NEXT</t>
+          <t>PLAQUETA POTENCIA GAFA/ELECTROLUX 6000/7000/6500/7500</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -22190,17 +22190,17 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>538-503-3</t>
+          <t>504-9803389-9</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>CONTACTOR DILETTA 25A 220V 1NA</t>
+          <t>PLAQUETA DISPLAY LED DREAN NEXT</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>$37.700</t>
+          <t>$38.000</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -22215,12 +22215,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>37.700</t>
+          <t>38.000</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -22248,17 +22248,17 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>535-620-0</t>
+          <t>538-503-3</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>PRESOSTATO CHEVROLET GM/RENAULT/PEUGEOT</t>
+          <t>CONTACTOR DILETTA 25A 220V 1NA</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>$37.500</t>
+          <t>$37.700</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -22273,12 +22273,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>37.500</t>
+          <t>37.700</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>46.50</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
@@ -22306,17 +22306,17 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>535-2038-8</t>
+          <t>535-620-0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>VALVULA BLOCK TOYOTA HILUX 2.8 L/N</t>
+          <t>PRESOSTATO CHEVROLET GM/RENAULT/PEUGEOT</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>$37.100</t>
+          <t>$37.500</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -22331,12 +22331,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>37.100</t>
+          <t>37.500</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>46.50</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
@@ -22364,12 +22364,12 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>535-1632-2</t>
+          <t>535-2038-8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>TAPA EMBRAGUE CVC 12X105 (37D-MA)</t>
+          <t>VALVULA BLOCK TOYOTA HILUX 2.8 L/N</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -22422,17 +22422,17 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>548-204-4</t>
+          <t>535-1632-2</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>NIVEL DE ALUMINIO 60MM - IRIMO</t>
+          <t>TAPA EMBRAGUE CVC 12X105 (37D-MA)</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>$37.000</t>
+          <t>$37.100</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -22447,12 +22447,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>37.000</t>
+          <t>37.100</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.00</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -22480,12 +22480,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>560-551-1</t>
+          <t>548-204-4</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>MANIJA AMERIC.CARNICERA CROMADA</t>
+          <t>NIVEL DE ALUMINIO 60MM - IRIMO</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -22538,12 +22538,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>502-701-1</t>
+          <t>560-551-1</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>FORZ.ELCO N16-30 S/PALA 300 MM</t>
+          <t>MANIJA AMERIC.CARNICERA CROMADA</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -22596,12 +22596,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2149-205-014</t>
+          <t>502-701-1</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>CONTROL DIG.TEMP. 1SO/1SA MT-512E 220V</t>
+          <t>FORZ.ELCO N16-30 S/PALA 300 MM</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -22654,17 +22654,17 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>524-604-4</t>
+          <t>2149-205-014</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>RESISTENCIA HELADERA PATRICK-FAGOR 814 EL ART.604</t>
+          <t>CONTROL DIG.TEMP. 1SO/1SA MT-512E 220V</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>$36.828</t>
+          <t>$37.000</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -22679,12 +22679,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>36.828</t>
+          <t>37.000</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22712,17 +22712,17 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>535-480-0</t>
+          <t>524-604-4</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>SELLADOR DE FUGAS P/ R 134</t>
+          <t>RESISTENCIA HELADERA PATRICK-FAGOR 814 EL ART.604</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>$36.500</t>
+          <t>$36.828</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -22737,12 +22737,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>36.500</t>
+          <t>36.828</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22770,17 +22770,17 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>3444-610-0</t>
+          <t>535-480-0</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>CONTROL DIGITAL ELITECH EK610 1SO/1SA 220V</t>
+          <t>SELLADOR DE FUGAS P/ R 134</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>$35.500</t>
+          <t>$36.500</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -22795,12 +22795,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>35.500</t>
+          <t>36.500</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>45.26</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22828,12 +22828,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>560-568-0</t>
+          <t>3444-610-0</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>MANIJA AMERICANA CROMADA</t>
+          <t>CONTROL DIGITAL ELITECH EK610 1SO/1SA 220V</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -22886,17 +22886,17 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>513-8282-1</t>
+          <t>560-568-0</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>MENSULA 82 CM. EL PAR  BLANCAS</t>
+          <t>MANIJA AMERICANA CROMADA</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>$35.400</t>
+          <t>$35.500</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -22911,12 +22911,12 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>35.400</t>
+          <t>35.500</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>43.90</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22944,17 +22944,17 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>530-1299-9</t>
+          <t>513-8282-1</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>PLAQUETA UNIVERSAL PARA HELADERAS</t>
+          <t>MENSULA 82 CM. EL PAR  BLANCAS</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>$35.000</t>
+          <t>$35.400</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -22969,12 +22969,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>35.000</t>
+          <t>35.400</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>43.40</t>
+          <t>43.90</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>548-1001-1</t>
+          <t>530-1299-9</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>DESTORNILLADORES BAHCO SET X 6</t>
+          <t>PLAQUETA UNIVERSAL PARA HELADERAS</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -23060,12 +23060,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>550-112-2</t>
+          <t>548-1001-1</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>DESENGRASANTE "DUCH-A"  5KG</t>
+          <t>DESTORNILLADORES BAHCO SET X 6</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -23118,12 +23118,12 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>3444-10-0</t>
+          <t>550-112-2</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>CONTROL DIGITAL ELITECH STC1000X</t>
+          <t>DESENGRASANTE "DUCH-A"  5KG</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -23176,12 +23176,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504-1023582-2</t>
+          <t>3444-10-0</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>EJE CENTRIFUGO DREAN CONCEPT 5.05-FUZZI</t>
+          <t>CONTROL DIGITAL ELITECH STC1000X</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -23234,17 +23234,17 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>524-314-4</t>
+          <t>504-1023582-2</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>RESISTENCIA WHIRLPOOL ERG35D1 - 350W (A314)</t>
+          <t>EJE CENTRIFUGO DREAN CONCEPT 5.05-FUZZI</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>$34.753</t>
+          <t>$35.000</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -23259,12 +23259,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>34.753</t>
+          <t>35.000</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>43.40</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -23292,17 +23292,17 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>535-5020-0</t>
+          <t>524-314-4</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>RODAMIENTO NSK 35 BG05 35 X 50 X 20 (JAPON)</t>
+          <t>RESISTENCIA WHIRLPOOL ERG35D1 - 350W (A314)</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>$34.500</t>
+          <t>$34.753</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -23317,12 +23317,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>34.500</t>
+          <t>34.753</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -28782,17 +28782,17 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>513-6262-1</t>
+          <t>580-6306-1</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>MENSULA 62 CM. EL PAR BLANCAS</t>
+          <t>RULEMAN SKF 6306</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>$22.500</t>
+          <t>$22.600</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -28807,12 +28807,12 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>22.500</t>
+          <t>22.600</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
@@ -28840,12 +28840,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>522-1310-0</t>
+          <t>513-6262-1</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>RESISTENCIA SILICONADA TPC 45W X MTS</t>
+          <t>MENSULA 62 CM. EL PAR BLANCAS</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -28898,17 +28898,17 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504-2002-2</t>
+          <t>522-1310-0</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>AGITADOR JM 90</t>
+          <t>RESISTENCIA SILICONADA TPC 45W X MTS</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>$22.300</t>
+          <t>$22.500</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -28923,12 +28923,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>22.300</t>
+          <t>22.500</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -28956,17 +28956,17 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>523-2000-0</t>
+          <t>504-2002-2</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>RELOJ TIMER CODINI 4 CONTACTOS</t>
+          <t>AGITADOR JM 90</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>$22.100</t>
+          <t>$22.300</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -28981,12 +28981,12 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>22.100</t>
+          <t>22.300</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>27.40</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
@@ -29014,17 +29014,17 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>508-702-2</t>
+          <t>523-2000-0</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>ELECTROVALVULA PHILCO PH8/10/12-ELECTROLUX-LG</t>
+          <t>RELOJ TIMER CODINI 4 CONTACTOS</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>$22.000</t>
+          <t>$22.100</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -29039,12 +29039,12 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>22.000</t>
+          <t>22.100</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>27.40</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -29072,12 +29072,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>3027-7001-0</t>
+          <t>508-702-2</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>ACTUADOR FRENO GAFA/ELECTROLUX LEGITIMO</t>
+          <t>ELECTROVALVULA PHILCO PH8/10/12-ELECTROLUX-LG</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>532-137-7</t>
+          <t>3027-7001-0</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>RODAM.L/P. DREAN FAMILY</t>
+          <t>ACTUADOR FRENO GAFA/ELECTROLUX LEGITIMO</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -29188,17 +29188,17 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>530-9535-5</t>
+          <t>532-137-7</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>COBERTOR PARA SPLIT 18-24-36 BTU</t>
+          <t>RODAM.L/P. DREAN FAMILY</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>$21.900</t>
+          <t>$22.000</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -29213,12 +29213,12 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>21.900</t>
+          <t>22.000</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
@@ -29246,17 +29246,17 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>560-1565-5</t>
+          <t>530-9535-5</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>BLOQUE O TORRE - PUERTAS FRIGORIFICAS</t>
+          <t>COBERTOR PARA SPLIT 18-24-36 BTU</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>$21.800</t>
+          <t>$21.900</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -29271,12 +29271,12 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>21.800</t>
+          <t>21.900</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
@@ -29304,17 +29304,17 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>535-203-3</t>
+          <t>560-1565-5</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>FILTRO DESHIDRATANTE TOYOTA PALIO GOL SIENA</t>
+          <t>BLOQUE O TORRE - PUERTAS FRIGORIFICAS</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>$21.500</t>
+          <t>$21.800</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -29329,12 +29329,12 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>21.500</t>
+          <t>21.800</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
@@ -29362,12 +29362,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504-1020308-8</t>
+          <t>535-203-3</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>TAPA DREAN FAMILY 046/56/66/76/86/96</t>
+          <t>FILTRO DESHIDRATANTE TOYOTA PALIO GOL SIENA</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -29420,12 +29420,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>530-1005-5</t>
+          <t>504-1020308-8</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>RELAY EMBRACO CORTO + PROTECTOR 1/3+</t>
+          <t>TAPA DREAN FAMILY 046/56/66/76/86/96</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -29478,12 +29478,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>580-6306-1</t>
+          <t>530-1005-5</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>RULEMAN SKF 6306</t>
+          <t>RELAY EMBRACO CORTO + PROTECTOR 1/3+</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>507-234-4</t>
+          <t>580-6305-1</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>AUTOMATICO ROBERTSHAW RC 22036-4</t>
+          <t>RULEMAN SKF 6305</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -33573,14 +33573,10 @@
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -33596,17 +33592,17 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>2000-290-1</t>
+          <t>507-234-4</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>ACEITE REFRIOIL R290 - 1 LITRO</t>
+          <t>AUTOMATICO ROBERTSHAW RC 22036-4</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>$16.740</t>
+          <t>$16.800</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -33621,12 +33617,12 @@
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>16.740</t>
+          <t>16.800</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
@@ -33654,17 +33650,17 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>506-521-0</t>
+          <t>2000-290-1</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>BISAGRA MOD.K CROMADA</t>
+          <t>ACEITE REFRIOIL R290 - 1 LITRO</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>$16.500</t>
+          <t>$16.740</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -33679,12 +33675,12 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>16.500</t>
+          <t>16.740</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K577" t="inlineStr">
@@ -33712,12 +33708,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>506-300-0</t>
+          <t>506-521-0</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>BISAGRA FREEZER GAFA 200/300</t>
+          <t>BISAGRA MOD.K CROMADA</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -33770,12 +33766,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>538-60-0</t>
+          <t>506-300-0</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>TERMOM.ANALOG.-40+40º 60MM P/PANEL</t>
+          <t>BISAGRA FREEZER GAFA 200/300</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -33828,12 +33824,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>522-250-0</t>
+          <t>538-60-0</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>FORZ.IMPORTADO P/PALA 250MM 10 WATTS</t>
+          <t>TERMOM.ANALOG.-40+40º 60MM P/PANEL</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -33886,12 +33882,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>572-9080-0</t>
+          <t>522-250-0</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>PISTON ACURREITOR 080 9000 FRIO</t>
+          <t>FORZ.IMPORTADO P/PALA 250MM 10 WATTS</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -33944,12 +33940,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>572-9088-8</t>
+          <t>572-9080-0</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>PISTON ACURREITOR 088 15000 FRIO CALOR</t>
+          <t>PISTON ACURREITOR 080 9000 FRIO</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -34002,12 +33998,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>572-9096-6</t>
+          <t>572-9088-8</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>PISTON ACURREITOR 096 15000 CALOR</t>
+          <t>PISTON ACURREITOR 088 15000 FRIO CALOR</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -34060,12 +34056,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>530-9532-2</t>
+          <t>572-9096-6</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>COBERTOR PARA SPLIT 9-12-18 BTU</t>
+          <t>PISTON ACURREITOR 096 15000 CALOR</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -34118,12 +34114,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>520-600-0</t>
+          <t>530-9532-2</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>TURBINA TANGENCIAL 180MM DERECHA</t>
+          <t>COBERTOR PARA SPLIT 9-12-18 BTU</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -34176,12 +34172,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>538-721-1</t>
+          <t>520-600-0</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>PROTECTOR DE TENSION -1500w</t>
+          <t>TURBINA TANGENCIAL 180MM DERECHA</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -34234,17 +34230,17 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>548-126001-1</t>
+          <t>538-721-1</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>ALICATE CORTE DIAGONAL  6 "</t>
+          <t>PROTECTOR DE TENSION -1500w</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>$16.000</t>
+          <t>$16.500</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -34259,12 +34255,12 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>16.500</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="K587" t="inlineStr">
@@ -34292,12 +34288,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>525-1123-3</t>
+          <t>548-126001-1</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>PROTECTOR MOTOR ROTATIVO 6000</t>
+          <t>ALICATE CORTE DIAGONAL  6 "</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
@@ -34350,12 +34346,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>525-1122-2</t>
+          <t>525-1123-3</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>PROTECTOR MOTOR ROTATIVO 4500</t>
+          <t>PROTECTOR MOTOR ROTATIVO 6000</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
@@ -34408,12 +34404,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>525-1120-0</t>
+          <t>525-1122-2</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>PROTECTOR MOTOR ROTATIVO 2250</t>
+          <t>PROTECTOR MOTOR ROTATIVO 4500</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -34466,12 +34462,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>538-793-3</t>
+          <t>525-1120-0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>LLAVE TERMICA TETRAPOLAR 4X32</t>
+          <t>PROTECTOR MOTOR ROTATIVO 2250</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -34524,12 +34520,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>538-792-2</t>
+          <t>538-793-3</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>LLAVE TERMICA TETRAPOLAR 4X25</t>
+          <t>LLAVE TERMICA TETRAPOLAR 4X32</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
@@ -34582,12 +34578,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>538-791-1</t>
+          <t>538-792-2</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>LLAVE TERMICA TETRAPOLAR 4X20</t>
+          <t>LLAVE TERMICA TETRAPOLAR 4X25</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
@@ -34640,12 +34636,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>538-790-0</t>
+          <t>538-791-1</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>LLAVE TERMICA TETRAPOLAR 4X15</t>
+          <t>LLAVE TERMICA TETRAPOLAR 4X20</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -34698,12 +34694,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>525-1105-1</t>
+          <t>538-790-0</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>PROTECTOR TERMICO ACMAR 1.5T - 59VN36</t>
+          <t>LLAVE TERMICA TETRAPOLAR 4X15</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -34756,12 +34752,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>525-1100-6</t>
+          <t>525-1105-1</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>PROTECTOR TERMICO ACMAR 1/3 HP - 59V73</t>
+          <t>PROTECTOR TERMICO ACMAR 1.5T - 59VN36</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -34814,12 +34810,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>525-1113-1</t>
+          <t>525-1100-6</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>PROTECTOR TERMICO CSM - 32 * AJ 5512</t>
+          <t>PROTECTOR TERMICO ACMAR 1/3 HP - 59V73</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -34872,17 +34868,17 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>524-794-0</t>
+          <t>525-1113-1</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>RESISTENCIA HELADERA MARSHALL ART.1021 / 1001</t>
+          <t>PROTECTOR TERMICO CSM - 32 * AJ 5512</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>$15.967</t>
+          <t>$16.000</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -34897,12 +34893,12 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>15.967</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>19.80</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
@@ -34930,17 +34926,17 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>506-521-1</t>
+          <t>524-794-0</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>BISAGRA DINAX CROMADA</t>
+          <t>RESISTENCIA HELADERA MARSHALL ART.1021 / 1001</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>$15.800</t>
+          <t>$15.967</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -34955,12 +34951,12 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>15.800</t>
+          <t>15.967</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
@@ -34988,17 +34984,17 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>2306-4920-0</t>
+          <t>506-521-1</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>PINTURA ROSA/PLATA MATE X  312 GRS</t>
+          <t>BISAGRA DINAX CROMADA</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>$15.768</t>
+          <t>$15.800</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -35013,12 +35009,12 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>15.768</t>
+          <t>15.800</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
@@ -35046,17 +35042,17 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>548-202-2</t>
+          <t>2306-4920-0</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>KIT 8 LLAVES TORX T9-T40 - IRIMO</t>
+          <t>PINTURA ROSA/PLATA MATE X  312 GRS</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>$15.600</t>
+          <t>$15.768</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -35071,12 +35067,12 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>15.600</t>
+          <t>15.768</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
@@ -35104,17 +35100,17 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>506-609-9</t>
+          <t>548-202-2</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>BISAGRA FREEZER NEBA</t>
+          <t>KIT 8 LLAVES TORX T9-T40 - IRIMO</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>$15.500</t>
+          <t>$15.600</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -35129,12 +35125,12 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>15.500</t>
+          <t>15.600</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -35162,12 +35158,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2306-7886-6</t>
+          <t>506-609-9</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>PINTURA EPOXI BRILLANTE NEGRA</t>
+          <t>BISAGRA FREEZER NEBA</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -35220,12 +35216,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>2306-7881-1</t>
+          <t>2306-7886-6</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>PINTURA EPOXI BRILLANTE BLANCO</t>
+          <t>PINTURA EPOXI BRILLANTE NEGRA</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
@@ -35278,12 +35274,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>513-5252-1</t>
+          <t>2306-7881-1</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>MENSULA 52/49 CM. EL PAR BLANCAS</t>
+          <t>PINTURA EPOXI BRILLANTE BLANCO</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -35336,12 +35332,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>580-6305-1</t>
+          <t>513-5252-1</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>RULEMAN SKF 6305</t>
+          <t>MENSULA 52/49 CM. EL PAR BLANCAS</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
@@ -35371,10 +35367,14 @@
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L606" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -38050,12 +38050,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>535-1661-1</t>
+          <t>525-1354-4</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>RODAMIENTO 35-BD-219 (35X55X20)</t>
+          <t>PROTECTOR TERMICO NRP 00 * AJ 2430 AKL19 - 3/4HP</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -38108,12 +38108,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>525-1354-4</t>
+          <t>525-1347-8</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>PROTECTOR TERMICO NRP 00 * AJ 2430 AKL19 - 3/4HP</t>
+          <t>RELAY - 145 (1/3+)</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -38166,12 +38166,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>525-1347-8</t>
+          <t>571-298-8</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>RELAY - 145 (1/3+)</t>
+          <t>TAPA TRANSP.SECARR.CODINI 2000</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -38224,12 +38224,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>571-298-8</t>
+          <t>507-237-7</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>TAPA TRANSP.SECARR.CODINI 2000</t>
+          <t>AUTOMATICO RC 45070-4 AMBIENTE</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -38282,12 +38282,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>507-237-7</t>
+          <t>504-1022212-2</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>AUTOMATICO RC 45070-4 AMBIENTE</t>
+          <t>TERMOACTUADOR DREAN CONCEPT</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -38340,12 +38340,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504-1022212-2</t>
+          <t>504-202030-0</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>TERMOACTUADOR DREAN CONCEPT</t>
+          <t>CABLE FRENO SEC.DREAN QV 5.5 / 6.5</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -38375,14 +38375,10 @@
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L658" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -38398,12 +38394,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504-202030-0</t>
+          <t>507-16-6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>CABLE FRENO SEC.DREAN QV 5.5 / 6.5</t>
+          <t>AUTOMATICO GAFA KDF26.1</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -38433,10 +38429,14 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L659" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -38452,17 +38452,17 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>507-16-6</t>
+          <t>504-1052631-1</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>AUTOMATICO GAFA KDF26.1</t>
+          <t>PRESOSTATO DR BLUE - AUTOBALANCE 125/85 350 RAST 5</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>$13.000</t>
+          <t>$12.960</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -38477,12 +38477,12 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>13.000</t>
+          <t>12.960</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -38510,17 +38510,17 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504-1052631-1</t>
+          <t>538-774-4</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>PRESOSTATO DR BLUE - AUTOBALANCE 125/85 350 RAST 5</t>
+          <t>LLAVE TERMICA TRIPOLAR 3X10</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>$12.960</t>
+          <t>$12.900</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -38535,12 +38535,12 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>12.960</t>
+          <t>12.900</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
@@ -38568,17 +38568,17 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>538-774-4</t>
+          <t>540-25-0</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>LLAVE TERMICA TRIPOLAR 3X10</t>
+          <t>POXILINA  250G</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>$12.900</t>
+          <t>$12.700</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -38593,12 +38593,12 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>12.900</t>
+          <t>12.700</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
@@ -38626,12 +38626,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>540-25-0</t>
+          <t>502-5612-2</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>POXILINA  250G</t>
+          <t>MINI CORTADORA DE CAÑO</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -38684,17 +38684,17 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>502-5612-2</t>
+          <t>3027-6069-7</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>MINI CORTADORA DE CAÑO</t>
+          <t>PLACA MEMBRANA GAFA/ELECTROLUX 6000/7000</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>$12.700</t>
+          <t>$12.636</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -38709,12 +38709,12 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>12.700</t>
+          <t>12.636</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
@@ -38742,17 +38742,17 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>3027-6069-7</t>
+          <t>548-203-3</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>PLACA MEMBRANA GAFA/ELECTROLUX 6000/7000</t>
+          <t>CUTTER 18MM - IRIMO</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>$12.636</t>
+          <t>$12.600</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -38767,12 +38767,12 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>12.636</t>
+          <t>12.600</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -38800,12 +38800,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>548-203-3</t>
+          <t>532-68-8</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>CUTTER 18MM - IRIMO</t>
+          <t>ELECTROVALVULA 2 VIAS 90 UNIVERSAL</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
@@ -38835,14 +38835,10 @@
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L666" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -38858,12 +38854,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>532-68-8</t>
+          <t>508-703-3</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>ELECTROVALVULA 2 VIAS 90 UNIVERSAL</t>
+          <t>ELECTROVALVULA 2 VIAS 180 UNIVERSAL</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
@@ -38912,17 +38908,17 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>508-703-3</t>
+          <t>2137-33-3</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>ELECTROVALVULA 2 VIAS 180 UNIVERSAL</t>
+          <t>PULVERIZADOR A PRESION X 3 LTS</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>$12.600</t>
+          <t>$12.500</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -38937,20 +38933,24 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>12.600</t>
+          <t>12.500</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L668" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -38966,12 +38966,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>2137-33-3</t>
+          <t>532-2123-7</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>PULVERIZADOR A PRESION X 3 LTS</t>
+          <t>PLAQ. BAJA DE ESTATOR SENS.DE MOVIM.LG</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
@@ -39024,12 +39024,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>532-2123-7</t>
+          <t>504-202023-3</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>PLAQ. BAJA DE ESTATOR SENS.DE MOVIM.LG</t>
+          <t>BASE TAPA SEC. DREAN  QV 6.5</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -39082,12 +39082,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504-202023-3</t>
+          <t>530-90165-0</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>BASE TAPA SEC. DREAN  QV 6.5</t>
+          <t>FILTRO ALCO 165 5/8F</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
@@ -39140,12 +39140,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>530-90165-0</t>
+          <t>502-600-L</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 165 5/8F</t>
+          <t>LATA R600 NECTON/BLUESTAR 420 GRS</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -39198,17 +39198,17 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>502-600-L</t>
+          <t>538-398-8</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>LATA R600 NECTON/BLUESTAR 420 GRS</t>
+          <t>PULSADOR DE EMERGENCIA CON GIRO NC</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>$12.500</t>
+          <t>$12.204</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -39223,12 +39223,12 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>12.500</t>
+          <t>12.204</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
@@ -39256,17 +39256,17 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>538-398-8</t>
+          <t>535-825-5</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>PULSADOR DE EMERGENCIA CON GIRO NC</t>
+          <t>SELLO COMPRESOR .GM/DELPHI CVC (35M-NA)</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>$12.204</t>
+          <t>$12.200</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -39281,7 +39281,7 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>12.204</t>
+          <t>12.200</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -39314,12 +39314,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>535-825-5</t>
+          <t>535-817-7</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>SELLO COMPRESOR .GM/DELPHI CVC (35M-NA)</t>
+          <t>SELLO DELPHI CVC MINI (35M-MA)</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
@@ -39372,17 +39372,17 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>535-817-7</t>
+          <t>530-317-7</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>SELLO DELPHI CVC MINI (35M-MA)</t>
+          <t>VALVULA SPLIT 1/2 GGT-604</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>$12.200</t>
+          <t>$12.100</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>12.200</t>
+          <t>12.100</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
@@ -39430,17 +39430,17 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>530-317-7</t>
+          <t>530-12-12</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>VALVULA SPLIT 1/2 GGT-604</t>
+          <t>VALVULA CHECK P/SPLIT 1/2</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>$12.100</t>
+          <t>$12.096</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -39455,7 +39455,7 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>12.100</t>
+          <t>12.096</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -39488,17 +39488,17 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>530-12-12</t>
+          <t>532-36654-4</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>VALVULA CHECK P/SPLIT 1/2</t>
+          <t>EJE MAZA IZQUIERDO DR.GOLD</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>$12.096</t>
+          <t>$12.000</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -39513,12 +39513,12 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>12.096</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>532-36654-4</t>
+          <t>532-36653-3</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>EJE MAZA IZQUIERDO DR.GOLD</t>
+          <t>EJE MAZA DERECHO DR.GOLD</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
@@ -39604,12 +39604,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>532-36653-3</t>
+          <t>502-35-5</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>EJE MAZA DERECHO DR.GOLD</t>
+          <t>LLAVE T/GLOBO RECTA 1/4F</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
@@ -39662,12 +39662,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>502-35-5</t>
+          <t>508-708-8</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>LLAVE T/GLOBO RECTA 1/4F</t>
+          <t>ELECTROVALVULA SIMPLE PHILCO</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>508-708-8</t>
+          <t>3027-7020-4</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>ELECTROVALVULA SIMPLE PHILCO</t>
+          <t>POLEA C/VENTILADOR P/LAVARROPAS ELECTROLUX - GAFA</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -39778,12 +39778,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>3027-7020-4</t>
+          <t>508-202-2</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>POLEA C/VENTILADOR P/LAVARROPAS ELECTROLUX - GAFA</t>
+          <t>BISAGRA BOSCH ( CHICA )</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
@@ -39813,14 +39813,10 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -39836,12 +39832,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>508-202-2</t>
+          <t>504-1025783-3</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>BISAGRA BOSCH ( CHICA )</t>
+          <t>CONJ.BISAGRA DR.BLUE - 180</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
@@ -39871,10 +39867,14 @@
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L684" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -39890,12 +39890,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504-1025783-3</t>
+          <t>504-202022-2</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>CONJ.BISAGRA DR.BLUE - 180</t>
+          <t>BASE TAPA SEC. DREAN QV 5.5</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
@@ -39948,12 +39948,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504-202022-2</t>
+          <t>538-22-2</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>BASE TAPA SEC. DREAN QV 5.5</t>
+          <t>TERMOMETRO DIGITAL PARA PANEL 220 V (VERDE)</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -40006,12 +40006,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>538-22-2</t>
+          <t>544-6050-4</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>TERMOMETRO DIGITAL PARA PANEL 220 V (VERDE)</t>
+          <t>FILTRO A.A.  600 X 500 X 40</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -40064,12 +40064,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>544-6050-4</t>
+          <t>504-9802525-5</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>FILTRO A.A.  600 X 500 X 40</t>
+          <t>BLOCAPUERTA DREAN NEXT 8.14 APERTURA INSTANT.</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -40122,12 +40122,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504-9802525-5</t>
+          <t>504-1026251-1</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>BLOCAPUERTA DREAN NEXT 8.14 APERTURA INSTANT.</t>
+          <t>ELECTROVALVULA 2 VIAS 180º DR.BLUE / DR. NEXT</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
@@ -40180,17 +40180,17 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504-1026251-1</t>
+          <t>2000-740-0</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>ELECTROVALVULA 2 VIAS 180º DR.BLUE / DR. NEXT</t>
+          <t>LIMPIA CONDUCTOS A.A. SAFE AIR</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>$12.000</t>
+          <t>$11.900</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -40205,12 +40205,12 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>11.900</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -40238,12 +40238,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2000-740-0</t>
+          <t>543-111-0</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>LIMPIA CONDUCTOS A.A. SAFE AIR</t>
+          <t>BURLETE DOBLE BALON BLANCO 1450X750</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
@@ -40296,12 +40296,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>543-111-0</t>
+          <t>543-131-0</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>BURLETE DOBLE BALON BLANCO 1450X750</t>
+          <t>BURLETE DOBLE BALON GRIS 1450X750</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
@@ -40354,17 +40354,17 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>543-131-0</t>
+          <t>513-4242-1</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>BURLETE DOBLE BALON GRIS 1450X750</t>
+          <t>MENSULA 42/41 CM. EL PAR  BLANCAS</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>$11.900</t>
+          <t>$11.700</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -40379,12 +40379,12 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>11.900</t>
+          <t>11.700</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -40412,12 +40412,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>513-4242-1</t>
+          <t>581-27021-1</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>MENSULA 42/41 CM. EL PAR  BLANCAS</t>
+          <t>RODAMIENTO AWR680/CWR600 - SKF-KOYO 6006</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
@@ -42948,12 +42948,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>581-27021-1</t>
+          <t>513-311-1</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>RODAMIENTO AWR680/CWR600 - SKF-KOYO 6006</t>
+          <t>CINTA ALUMINIO 50 MTS. X  50MM C/ADHES</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
@@ -42983,14 +42983,10 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -43006,12 +43002,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>513-311-1</t>
+          <t>558-101107-3</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>CINTA ALUMINIO 50 MTS. X  50MM C/ADHES</t>
+          <t>CAPACITOR SICAP 101/107 330 V</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
@@ -43041,10 +43037,14 @@
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L739" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -43060,12 +43060,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>558-101107-3</t>
+          <t>508-1317-8</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>CAPACITOR SICAP 101/107 330 V</t>
+          <t>CORREA 1317 POLI-V 8PJ DR FAMILY 046-056-086</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
@@ -43118,17 +43118,17 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>508-1317-8</t>
+          <t>2000-5-5</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>CORREA 1317 POLI-V 8PJ DR FAMILY 046-056-086</t>
+          <t>ACEITE REFRIOIL 5GS X LITRO</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>$10.500</t>
+          <t>$10.476</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -43143,24 +43143,20 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>10.500</t>
+          <t>10.476</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -43176,12 +43172,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2000-5-5</t>
+          <t>508-202-5</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>ACEITE REFRIOIL 5GS X LITRO</t>
+          <t>BISAGRA BOSCH-ZENITH</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
@@ -43211,10 +43207,14 @@
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L742" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -43230,17 +43230,17 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>508-202-5</t>
+          <t>530-90083-9</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>BISAGRA BOSCH-ZENITH</t>
+          <t>FILTRO ALCO 083 3/8S</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>$10.476</t>
+          <t>$10.400</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -43255,12 +43255,12 @@
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>10.476</t>
+          <t>10.400</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
@@ -43288,12 +43288,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>530-90083-9</t>
+          <t>540-90-0</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 083 3/8S</t>
+          <t>POXIRAN 90 Gr</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
@@ -43346,12 +43346,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>540-90-0</t>
+          <t>530-90083-0</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>POXIRAN 90 Gr</t>
+          <t>FILTRO ALCO 083 3/8F</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
@@ -43404,17 +43404,17 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>530-90083-0</t>
+          <t>544-7949-2</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 083 3/8F</t>
+          <t>FILTRO A.A.  790 X 490 X 20</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>$10.400</t>
+          <t>$10.368</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -43429,12 +43429,12 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>10.400</t>
+          <t>10.368</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
@@ -43462,17 +43462,17 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>544-7949-2</t>
+          <t>530-90082-9</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>FILTRO A.A.  790 X 490 X 20</t>
+          <t>FILTRO ALCO 082 1/4S</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>$10.368</t>
+          <t>$10.300</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -43487,12 +43487,12 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>10.368</t>
+          <t>10.300</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
@@ -43520,12 +43520,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>530-90082-9</t>
+          <t>530-90082-0</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 082 1/4S</t>
+          <t>FILTRO ALCO 082 1/4F</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
@@ -43578,17 +43578,17 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>530-90082-0</t>
+          <t>530-90053-9</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 082 1/4F</t>
+          <t>FILTRO ALCO 053 3/8S</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>$10.300</t>
+          <t>$10.200</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -43603,12 +43603,12 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>10.300</t>
+          <t>10.200</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
@@ -43636,17 +43636,17 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>530-90053-9</t>
+          <t>3027-4028-0</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 053 3/8S</t>
+          <t>CODO UNION LAVARROPAS GAFA/ELECTROLUX 7000/7500</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>$10.200</t>
+          <t>$10.100</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -43661,12 +43661,12 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>10.200</t>
+          <t>10.100</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
@@ -43694,17 +43694,17 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>3027-4028-0</t>
+          <t>530-38-38</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>CODO UNION LAVARROPAS GAFA/ELECTROLUX 7000/7500</t>
+          <t>VALVULA CHECK P/ SPLIT 3/8</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>$10.100</t>
+          <t>$10.044</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -43719,12 +43719,12 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>10.100</t>
+          <t>10.044</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
@@ -43752,17 +43752,17 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>530-38-38</t>
+          <t>530-90164-9</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>VALVULA CHECK P/ SPLIT 3/8</t>
+          <t>FILTRO ALCO 164 1/2S</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>$10.044</t>
+          <t>$10.000</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -43777,12 +43777,12 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>10.044</t>
+          <t>10.000</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.40</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
@@ -43810,12 +43810,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>530-90164-9</t>
+          <t>504-9802670-0</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 164 1/2S</t>
+          <t>BLOCAPUERTA DREAN NEXT APERTURA NORMAL</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
@@ -43868,12 +43868,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504-9802670-0</t>
+          <t>508-1908-8</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>BLOCAPUERTA DREAN NEXT APERTURA NORMAL</t>
+          <t>BLOCAPUERTA LAVARROPAS DREAN - EXCELENT BLUE - AURORA - COVENTRY</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
@@ -43926,17 +43926,17 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>508-1908-8</t>
+          <t>544-6560-4</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>BLOCAPUERTA LAVARROPAS DREAN - EXCELENT BLUE - AURORA - COVENTRY</t>
+          <t>FILTRO A.A.  650 X 600 X 40</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>$10.000</t>
+          <t>$9.936</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -43951,12 +43951,12 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>10.000</t>
+          <t>9.936</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>12.40</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
@@ -43984,17 +43984,17 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>544-6560-4</t>
+          <t>502-94051-2</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>FILTRO A.A.  650 X 600 X 40</t>
+          <t>AUT.BS.RC 94051-2  3TERM.CAP 102</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>$9.936</t>
+          <t>$9.900</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -44009,12 +44009,12 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>9.936</t>
+          <t>9.900</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
@@ -44042,12 +44042,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>502-94051-2</t>
+          <t>515-199-4</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>AUT.BS.RC 94051-2  3TERM.CAP 102</t>
+          <t>BLOCAPUERTA LG 3 CONT ATMA/PHILCO</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
@@ -44077,14 +44077,10 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L757" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -44100,12 +44096,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>515-199-4</t>
+          <t>530-615-5</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>BLOCAPUERTA LG 3 CONT ATMA/PHILCO</t>
+          <t>CORTADORA DE CAÑO IMPORTADA GT274</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
@@ -44135,10 +44131,14 @@
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L758" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -44154,17 +44154,17 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>530-615-5</t>
+          <t>2000-4-4</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>CORTADORA DE CAÑO IMPORTADA GT274</t>
+          <t>ACEITE REFRIOIL 4GS X LITRO</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>$9.900</t>
+          <t>$9.800</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -44179,24 +44179,20 @@
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>9.900</t>
+          <t>9.800</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L759" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -44212,12 +44208,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2000-4-4</t>
+          <t>502-552-2</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>ACEITE REFRIOIL 4GS X LITRO</t>
+          <t>ADAPTADOR 5/16 P/JERINGAS EXTREME</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
@@ -44247,10 +44243,14 @@
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L760" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -44266,12 +44266,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>502-552-2</t>
+          <t>502-551-1</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>ADAPTADOR 5/16 P/JERINGAS EXTREME</t>
+          <t>ADAPTADOR 1/4 P/JERINGAS EXTREME</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
@@ -44324,12 +44324,12 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>502-551-1</t>
+          <t>534-112-90</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>ADAPTADOR 1/4 P/JERINGAS EXTREME</t>
+          <t>CURVA DE COBRE 90° 1 1/2″</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
@@ -44382,12 +44382,12 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>534-112-90</t>
+          <t>2000-700-1</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>CURVA DE COBRE 90° 1 1/2″</t>
+          <t>AGENTE DE LIMPIEZA REFRIOIL CLEANER ACID X 1 LT</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
@@ -44440,17 +44440,17 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2000-700-1</t>
+          <t>544-6350-4</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>AGENTE DE LIMPIEZA REFRIOIL CLEANER ACID X 1 LT</t>
+          <t>FILTRO A.A.  630 X 500 X 40</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>$9.800</t>
+          <t>$9.720</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -44465,12 +44465,12 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>9.800</t>
+          <t>9.720</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -44498,12 +44498,12 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>544-6350-4</t>
+          <t>508-1200-8</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>FILTRO A.A.  630 X 500 X 40</t>
+          <t>CORREA 1200 H8 DR GOLD 6, 8 Y 10</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
@@ -44556,17 +44556,17 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>508-1200-8</t>
+          <t>522-1001-1</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>CORREA 1200 H8 DR GOLD 6, 8 Y 10</t>
+          <t>TIMER NOFROST BLANCO 6H X 21M</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>$9.720</t>
+          <t>$9.600</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -44581,12 +44581,12 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>9.720</t>
+          <t>9.600</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -44614,17 +44614,17 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>522-1001-1</t>
+          <t>570-342-2</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>TIMER NOFROST BLANCO 6H X 21M</t>
+          <t>RESIST.VIDRIO NO FROST  8" 200MM  115W</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>$9.600</t>
+          <t>$9.500</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -44639,12 +44639,12 @@
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>9.600</t>
+          <t>9.500</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>11.90</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
@@ -44672,12 +44672,12 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>570-342-2</t>
+          <t>530-90163-9</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>RESIST.VIDRIO NO FROST  8" 200MM  115W</t>
+          <t>FILTRO ALCO 163 3/8S</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
@@ -44730,12 +44730,12 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>530-90163-9</t>
+          <t>530-316-6</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 163 3/8S</t>
+          <t>VALVULA SPLIT 3/8 GGT-603</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
@@ -44788,12 +44788,12 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>530-316-6</t>
+          <t>2000-180-0</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>VALVULA SPLIT 3/8 GGT-603</t>
+          <t>ACEITE REFRIOIL 180 X 1 LITRO</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
@@ -44846,12 +44846,12 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>2000-180-0</t>
+          <t>530-90164-0</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>ACEITE REFRIOIL 180 X 1 LITRO</t>
+          <t>FILTRO ALCO 164 1/2F</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
@@ -44904,12 +44904,12 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>530-90164-0</t>
+          <t>530-90163-0</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 164 1/2F</t>
+          <t>FILTRO ALCO 163 3/8F</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
@@ -44962,12 +44962,12 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>530-90163-0</t>
+          <t>502-4070-2</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>FILTRO ALCO 163 3/8F</t>
+          <t>AUTOMATICO BS.RFR 4070-2  DUAL GAFA-BAMBI 2TERM.CAP 101</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
@@ -45020,12 +45020,12 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>502-4070-2</t>
+          <t>508-1212-8</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RFR 4070-2  DUAL GAFA-BAMBI 2TERM.CAP 101</t>
+          <t>CORREA 1212 8PJ DR GOLD BLUE-AU-NEXT 6</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
@@ -45078,12 +45078,12 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>508-1212-8</t>
+          <t>502-45070-4</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>CORREA 1212 8PJ DR GOLD BLUE-AU-NEXT 6</t>
+          <t>AUTOMATICO BS.RC 45070-4 AMBIENTE</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
@@ -45136,12 +45136,12 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>502-45070-4</t>
+          <t>502-45070-2</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RC 45070-4 AMBIENTE</t>
+          <t>AUTOMATICO BS.RC 45070-2 AMB.GAFA / BEBED CAP 125</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
@@ -45194,12 +45194,12 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>502-45070-2</t>
+          <t>502-22036-6</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RC 45070-2 AMB.GAFA / BEBED CAP 125</t>
+          <t>AUTOMATICO BS.RC 22036 PATRICK 2 TERM.CAP 50</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
@@ -45252,12 +45252,12 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>502-22036-6</t>
+          <t>508-1-2</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RC 22036 PATRICK 2 TERM.CAP 50</t>
+          <t>MOTOR ELECTROBOMBA ASKOLL</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
@@ -45310,17 +45310,17 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>508-1-2</t>
+          <t>525-518-8</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>MOTOR ELECTROBOMBA ASKOLL</t>
+          <t>CONTROL REMOTO UNIVERSAL 6000 EN 1 CR-E08</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>$9.500</t>
+          <t>$9.300</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -45335,12 +45335,12 @@
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>9.500</t>
+          <t>9.300</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
@@ -45368,12 +45368,12 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>525-518-8</t>
+          <t>2000-32-5</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>CONTROL REMOTO UNIVERSAL 6000 EN 1 CR-E08</t>
+          <t>ACEITE REFRIOIL PAG 32 X  1/2 LT -R134</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
@@ -45426,17 +45426,17 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>2000-32-5</t>
+          <t>581-71975-5</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>ACEITE REFRIOIL PAG 32 X  1/2 LT -R134</t>
+          <t>INTERRUPTOR DOBLE WHIRLPOOL</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>$9.300</t>
+          <t>$9.200</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -45451,12 +45451,12 @@
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>9.300</t>
+          <t>9.200</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="K781" t="inlineStr">
@@ -45484,12 +45484,12 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>581-71975-5</t>
+          <t>530-315-5</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>INTERRUPTOR DOBLE WHIRLPOOL</t>
+          <t>VALVULA SPLIT 1/4 GGT-602</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
@@ -45542,17 +45542,17 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>530-315-5</t>
+          <t>532-213-3</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>VALVULA SPLIT 1/4 GGT-602</t>
+          <t>CENTRO PLASTICO ROTOR LG INVERTER C/SUP</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>$9.200</t>
+          <t>$9.144</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -45567,12 +45567,12 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>9.200</t>
+          <t>9.144</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>11.34</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
@@ -45600,17 +45600,17 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>532-213-3</t>
+          <t>504-9804496-6</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>CENTRO PLASTICO ROTOR LG INVERTER C/SUP</t>
+          <t>TAPA DREAN FAMILY 6 ECO</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>$9.144</t>
+          <t>$9.100</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
@@ -45625,12 +45625,12 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>9.144</t>
+          <t>9.100</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>11.34</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -45658,12 +45658,12 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>504-9804496-6</t>
+          <t>535-1663-3</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>TAPA DREAN FAMILY 6 ECO</t>
+          <t>RODAMIENTO 35 BD 5220 (35 X 52 X 20)</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
@@ -45716,17 +45716,17 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>530-5010-1</t>
+          <t>535-1660-0</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH 50+10 MF DUAL</t>
+          <t>RODAMIENTO 35-BG05-S7G (35X50X20)</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>$9.072</t>
+          <t>$9.100</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -45741,12 +45741,12 @@
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>9.072</t>
+          <t>9.100</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
@@ -45774,17 +45774,17 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>530-5168-8</t>
+          <t>535-1661-1</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>VALVULA BOLA 5/16MF X 1/4HF C/RETENCION C/U</t>
+          <t>RODAMIENTO 35-BD-219 (35X55X20)</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>$9.000</t>
+          <t>$9.100</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -45799,12 +45799,12 @@
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>9.000</t>
+          <t>9.100</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="K787" t="inlineStr">
@@ -45832,17 +45832,17 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>530-1515-5</t>
+          <t>530-5010-1</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>VALVULA BOLA 1/4MF X 1/4HF C/RETENCION C/U</t>
+          <t>CAPACITOR COOLTECH 50+10 MF DUAL</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>$9.000</t>
+          <t>$9.072</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -45857,12 +45857,12 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>9.000</t>
+          <t>9.072</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
@@ -45890,12 +45890,12 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>567-632-2</t>
+          <t>530-5168-8</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>MANGUERA CARGA GAS  150 CMS S/TEE P/R410 C/U</t>
+          <t>VALVULA BOLA 5/16MF X 1/4HF C/RETENCION C/U</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
@@ -45948,12 +45948,12 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>532-528-8</t>
+          <t>530-1515-5</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>FILTRO PELUSA LAVARROPA LG REDONDO C/SUP</t>
+          <t>VALVULA BOLA 1/4MF X 1/4HF C/RETENCION C/U</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
@@ -46006,12 +46006,12 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>3027-248-8</t>
+          <t>567-632-2</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>BANDEJA EVAPORACION GAFA C/GRAMPAS</t>
+          <t>MANGUERA CARGA GAS  150 CMS S/TEE P/R410 C/U</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
@@ -46064,12 +46064,12 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>502-23669-4</t>
+          <t>532-528-8</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>AUT.BS.RC 23669-4 .2TERM.CAP 90 1/2C</t>
+          <t>FILTRO PELUSA LAVARROPA LG REDONDO C/SUP</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
@@ -46122,12 +46122,12 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>525-16-6</t>
+          <t>3027-248-8</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>PROTECTOR *GENERICO* 1/6</t>
+          <t>BANDEJA EVAPORACION GAFA C/GRAMPAS</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
@@ -46157,10 +46157,14 @@
       </c>
       <c r="K793" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L793" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -46176,12 +46180,12 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>585-119-9</t>
+          <t>502-23669-4</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>TERMOMETRO ALC.PLA.380X65 -30+50  ET690</t>
+          <t>AUT.BS.RC 23669-4 .2TERM.CAP 90 1/2C</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
@@ -46234,12 +46238,12 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>569-1093-3</t>
+          <t>525-16-6</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>VARILLA BRONCE REDONDA 2MM</t>
+          <t>PROTECTOR *GENERICO* 1/6</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
@@ -46269,14 +46273,10 @@
       </c>
       <c r="K795" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L795" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -46292,12 +46292,12 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>502-22027-2</t>
+          <t>585-119-9</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RC 22027-2 PATRICK 2 TERM. CAP 50</t>
+          <t>TERMOMETRO ALC.PLA.380X65 -30+50  ET690</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
@@ -46350,12 +46350,12 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>502-13646-6</t>
+          <t>569-1093-3</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>AUTOMATICO BS.RC 13646-2 =TF7 CAP 90</t>
+          <t>VARILLA BRONCE REDONDA 2MM</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -46408,17 +46408,17 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>2306-7792-2</t>
+          <t>502-22027-2</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>PINTURA ANTICORROSIVO  3 EN 1 EN AEROSOL</t>
+          <t>AUTOMATICO BS.RC 22027-2 PATRICK 2 TERM. CAP 50</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>$8.900</t>
+          <t>$9.000</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
@@ -46433,12 +46433,12 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>8.900</t>
+          <t>9.000</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
@@ -46466,17 +46466,17 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>530-201-1</t>
+          <t>502-13646-6</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>PINZA SELLADORA  IMPORTADA</t>
+          <t>AUTOMATICO BS.RC 13646-2 =TF7 CAP 90</t>
         </is>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>$8.900</t>
+          <t>$9.000</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
@@ -46491,12 +46491,12 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>8.900</t>
+          <t>9.000</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
@@ -46524,17 +46524,17 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>580-6204-4</t>
+          <t>2306-7792-2</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>RULEMAN SKF 6204</t>
+          <t>PINTURA ANTICORROSIVO  3 EN 1 EN AEROSOL</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>$8.800</t>
+          <t>$8.900</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
@@ -46549,20 +46549,24 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>8.800</t>
+          <t>8.900</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L800" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -46578,17 +46582,17 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>508-1138-7</t>
+          <t>530-201-1</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>CORREA 1138 POLI-V H7</t>
+          <t>PINZA SELLADORA  IMPORTADA</t>
         </is>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>$8.748</t>
+          <t>$8.900</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
@@ -46603,20 +46607,24 @@
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>8.748</t>
+          <t>8.900</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L801" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -46632,17 +46640,17 @@
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>2000-730-0</t>
+          <t>580-6204-4</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>AGENTE DE LIMPIEZA REFRIOIL MOT/SERPENTINA X 1 LT</t>
+          <t>RULEMAN SKF 6204</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>$8.700</t>
+          <t>$8.800</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
@@ -46657,24 +46665,20 @@
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>8.700</t>
+          <t>8.800</t>
         </is>
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="K802" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L802" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -46690,17 +46694,17 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>579-700-0</t>
+          <t>508-1138-7</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>POLIURETANO EN AEROSOL 250/300 ML</t>
+          <t>CORREA 1138 POLI-V H7</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>$8.700</t>
+          <t>$8.748</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
@@ -46715,24 +46719,20 @@
       </c>
       <c r="I803" t="inlineStr">
         <is>
-          <t>8.700</t>
+          <t>8.748</t>
         </is>
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="K803" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L803" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -46748,12 +46748,12 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>530-5006-0</t>
+          <t>2000-730-0</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH 50+6 MF DUAL</t>
+          <t>AGENTE DE LIMPIEZA REFRIOIL MOT/SERPENTINA X 1 LT</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
@@ -46806,17 +46806,17 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>534-50-0</t>
+          <t>579-700-0</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>FILTRO TORP. C/CHICOTE  50GR MOLECULAR</t>
+          <t>POLIURETANO EN AEROSOL 250/300 ML</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>$8.640</t>
+          <t>$8.700</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
@@ -46831,12 +46831,12 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>8.640</t>
+          <t>8.700</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
@@ -46864,17 +46864,17 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>571-502-2</t>
+          <t>530-5006-0</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>CABLE FRENO KOHINOOR 2062</t>
+          <t>CAPACITOR COOLTECH 50+6 MF DUAL</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>$8.600</t>
+          <t>$8.700</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
@@ -46889,12 +46889,12 @@
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>8.600</t>
+          <t>8.700</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
@@ -46922,17 +46922,17 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>571-502-3</t>
+          <t>534-50-0</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>CABLE FRENO KOHINOOR 2052</t>
+          <t>FILTRO TORP. C/CHICOTE  50GR MOLECULAR</t>
         </is>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>$8.600</t>
+          <t>$8.640</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
@@ -46947,12 +46947,12 @@
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>8.600</t>
+          <t>8.640</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
@@ -46980,12 +46980,12 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>571-502-4</t>
+          <t>571-502-2</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>CABLE FRENO KOHINOOR 2042</t>
+          <t>CABLE FRENO KOHINOOR 2062</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
@@ -47038,17 +47038,17 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>581-28026-6</t>
+          <t>571-502-3</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>RODAMIENTO DE ALTA VELOCIDAD AWG686/611</t>
+          <t>CABLE FRENO KOHINOOR 2052</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>$8.539</t>
+          <t>$8.600</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
@@ -47063,12 +47063,12 @@
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>8.539</t>
+          <t>8.600</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="K809" t="inlineStr">
@@ -47096,17 +47096,17 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>530-456-6</t>
+          <t>571-502-4</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH 45+6 MF DUAL</t>
+          <t>CABLE FRENO KOHINOOR 2042</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>$8.532</t>
+          <t>$8.600</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
@@ -47121,12 +47121,12 @@
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>8.532</t>
+          <t>8.600</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="K810" t="inlineStr">
@@ -47154,17 +47154,17 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>597-290-L</t>
+          <t>581-28026-6</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>LATA R290</t>
+          <t>RODAMIENTO DE ALTA VELOCIDAD AWG686/611</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>$8.500</t>
+          <t>$8.539</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
@@ -47179,12 +47179,12 @@
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>8.539</t>
         </is>
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="K811" t="inlineStr">
@@ -47212,17 +47212,17 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>530-521-1</t>
+          <t>530-456-6</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>ACOPLE RAPIDO L.ALTA ROJO R134</t>
+          <t>CAPACITOR COOLTECH 45+6 MF DUAL</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>$8.500</t>
+          <t>$8.532</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
@@ -47237,12 +47237,12 @@
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>8.532</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
@@ -47270,12 +47270,12 @@
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>530-520-0</t>
+          <t>597-290-L</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>ACOPLE RAPIDO L.BAJA AZUL R134</t>
+          <t>LATA R290</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
@@ -47328,12 +47328,12 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>535-1663-3</t>
+          <t>530-521-1</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>RODAMIENTO 35 BD 5220 (35 X 52 X 20)</t>
+          <t>ACOPLE RAPIDO L.ALTA ROJO R134</t>
         </is>
       </c>
       <c r="F814" t="inlineStr">
@@ -47386,12 +47386,12 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>535-1660-0</t>
+          <t>530-520-0</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>RODAMIENTO 35-BG05-S7G (35X50X20)</t>
+          <t>ACOPLE RAPIDO L.BAJA AZUL R134</t>
         </is>
       </c>
       <c r="F815" t="inlineStr">
@@ -61064,17 +61064,17 @@
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>534-1-58</t>
+          <t>504-1023576-6</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>REDUCCION COBRE 1" A 5/8"</t>
+          <t>RETEN EJE CENTRIFUGADO CONCEPT 5.05 M/N</t>
         </is>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t>$2.562</t>
+          <t>$2.600</t>
         </is>
       </c>
       <c r="G1052" t="inlineStr">
@@ -61089,12 +61089,12 @@
       </c>
       <c r="I1052" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="J1052" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="K1052" t="inlineStr">
@@ -61122,17 +61122,17 @@
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>548-200-0</t>
+          <t>504-1020017-7</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>KIT DE TACOS,TORNILLOS Y BULON PARA INSTALACIÓN</t>
+          <t>RETEN EJE CENTRIFUGADO CONCEPT</t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t>$2.550</t>
+          <t>$2.600</t>
         </is>
       </c>
       <c r="G1053" t="inlineStr">
@@ -61147,12 +61147,12 @@
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="J1053" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="K1053" t="inlineStr">
@@ -61180,17 +61180,17 @@
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>571-509-9</t>
+          <t>534-1-58</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>PALANCA KOHINOOR MODELO L600 (BLANCO/ VIOLETA/NEGRO)</t>
+          <t>REDUCCION COBRE 1" A 5/8"</t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t>$2.500</t>
+          <t>$2.562</t>
         </is>
       </c>
       <c r="G1054" t="inlineStr">
@@ -61205,12 +61205,12 @@
       </c>
       <c r="I1054" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.562</t>
         </is>
       </c>
       <c r="J1054" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="K1054" t="inlineStr">
@@ -61238,17 +61238,17 @@
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>534-78-8</t>
+          <t>548-200-0</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>UNION COBRE 7/8" P/SOLDAR</t>
+          <t>KIT DE TACOS,TORNILLOS Y BULON PARA INSTALACIÓN</t>
         </is>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
-          <t>$2.500</t>
+          <t>$2.550</t>
         </is>
       </c>
       <c r="G1055" t="inlineStr">
@@ -61263,20 +61263,24 @@
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J1055" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="K1055" t="inlineStr">
         <is>
-          <t>updated</t>
-        </is>
-      </c>
-      <c r="L1055" t="inlineStr"/>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -61292,12 +61296,12 @@
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>535-530-0</t>
+          <t>571-509-9</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>ORING GM 26,00 X 18,50 X 1,50  *44T-L</t>
+          <t>PALANCA KOHINOOR MODELO L600 (BLANCO/ VIOLETA/NEGRO)</t>
         </is>
       </c>
       <c r="F1056" t="inlineStr">
@@ -61350,12 +61354,12 @@
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>567-516-6</t>
+          <t>534-78-8</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>TUERCA 5/16 BRONCE TRAFILADA</t>
+          <t>UNION COBRE 7/8" P/SOLDAR</t>
         </is>
       </c>
       <c r="F1057" t="inlineStr">
@@ -61404,12 +61408,12 @@
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>504-1023610-0</t>
+          <t>535-530-0</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>TENSOR CUBA DREAN CONCEPT 5.05</t>
+          <t>ORING GM 26,00 X 18,50 X 1,50  *44T-L</t>
         </is>
       </c>
       <c r="F1058" t="inlineStr">
@@ -61462,12 +61466,12 @@
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>504-1023576-6</t>
+          <t>567-516-6</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>RETEN EJE CENTRIFUGADO CONCEPT 5.05 M/N</t>
+          <t>TUERCA 5/16 BRONCE TRAFILADA</t>
         </is>
       </c>
       <c r="F1059" t="inlineStr">
@@ -61497,14 +61501,10 @@
       </c>
       <c r="K1059" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="L1059" t="inlineStr">
-        <is>
-          <t>Code not found in ProductSupplier</t>
-        </is>
-      </c>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -61520,12 +61520,12 @@
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>504-1020017-7</t>
+          <t>504-1023610-0</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>RETEN EJE CENTRIFUGADO CONCEPT</t>
+          <t>TENSOR CUBA DREAN CONCEPT 5.05</t>
         </is>
       </c>
       <c r="F1060" t="inlineStr">
@@ -63608,12 +63608,12 @@
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>530-6-0</t>
+          <t>504-1026228-8</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH  6 MF</t>
+          <t>RETEN 47/25 DREAN BLUE (03-04)</t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
@@ -63666,17 +63666,17 @@
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>513-34-V</t>
+          <t>530-6-0</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>AISLACIÓN NEGRA D18   3/4" X 2MTS</t>
+          <t>CAPACITOR COOLTECH  6 MF</t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t>$1.800</t>
+          <t>$1.900</t>
         </is>
       </c>
       <c r="G1097" t="inlineStr">
@@ -63691,12 +63691,12 @@
       </c>
       <c r="I1097" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="J1097" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K1097" t="inlineStr">
@@ -63724,12 +63724,12 @@
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>530-5-0</t>
+          <t>513-34-V</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH  5 MF</t>
+          <t>AISLACIÓN NEGRA D18   3/4" X 2MTS</t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
@@ -63782,12 +63782,12 @@
       </c>
       <c r="D1099" t="inlineStr">
         <is>
-          <t>530-4-0</t>
+          <t>530-5-0</t>
         </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>CAPACITOR COOLTECH  4 MF</t>
+          <t>CAPACITOR COOLTECH  5 MF</t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
@@ -63840,17 +63840,17 @@
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>538-215-0</t>
+          <t>530-4-0</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>CABLE 2 X 1,50 MM T/TALLER X MT</t>
+          <t>CAPACITOR COOLTECH  4 MF</t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>$1.790</t>
+          <t>$1.800</t>
         </is>
       </c>
       <c r="G1100" t="inlineStr">
@@ -63865,12 +63865,12 @@
       </c>
       <c r="I1100" t="inlineStr">
         <is>
-          <t>1.790</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="J1100" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K1100" t="inlineStr">
@@ -63898,17 +63898,17 @@
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>513-58-V</t>
+          <t>538-215-0</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>AISLACIÓN NEGRA D15   5/8" X 2MTS</t>
+          <t>CABLE 2 X 1,50 MM T/TALLER X MT</t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>$1.700</t>
+          <t>$1.790</t>
         </is>
       </c>
       <c r="G1101" t="inlineStr">
@@ -63923,12 +63923,12 @@
       </c>
       <c r="I1101" t="inlineStr">
         <is>
-          <t>1.700</t>
+          <t>1.790</t>
         </is>
       </c>
       <c r="J1101" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K1101" t="inlineStr">
@@ -63956,12 +63956,12 @@
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>504-1026228-8</t>
+          <t>513-58-V</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>RETEN 47/25 DREAN BLUE (03-04)</t>
+          <t>AISLACIÓN NEGRA D15   5/8" X 2MTS</t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
